--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
@@ -452,7 +452,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Media.modifierExtension</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
@@ -370,7 +370,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -502,7 +502,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|CarePlan)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -528,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
     <t>高水準メディアカテゴリのコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-type</t>
+    <t>http://hl7.org/fhir/ValueSet/media-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -647,7 +647,7 @@
     <t>画像を収集する際に使用される投影イメージングビュー。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/media-view</t>
+    <t>http://hl7.org/fhir/ValueSet/media-view|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticImage.subjectOrientationCode</t>
@@ -792,7 +792,7 @@
     <t>メディアの理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -813,7 +813,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -847,7 +847,7 @@
     <t>Media.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric|Device)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1264,17 +1264,17 @@
   <dimension ref="A1:AQ32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="20.36328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.36328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.62109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="55.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1283,29 +1283,29 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.0390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="103.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="47.82421875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="71.20703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="49.83203125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="61.046875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="42.72265625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-media-endoscopy.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
